--- a/data/raw/PM/PM_fontenay sous bois.xlsx
+++ b/data/raw/PM/PM_fontenay sous bois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epfedu-my.sharepoint.com/personal/thibaut_martinantdepreneuf_epfedu_fr/Documents/Bureau/DefiAccessMaison/Prototype_Appli_DefisAccess/data/raw/PM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_74EE53A892AC479DEB199937E39CF018D6CE4651" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A76D11D7-55CA-47AE-9DC7-EF480CE75EF4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_74EE53A892AC479DEB199937E39CF018D6CE4651" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70AB59B2-71CF-4841-8416-6B7D643FBC4B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -857,6 +857,7 @@
   <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="62" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
   </cols>
